--- a/LAPORAN STOK/DATA STOK DVR.xlsx
+++ b/LAPORAN STOK/DATA STOK DVR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\LAPORAN STOK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\LAPORAN STOK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A9FE696-8EF6-4F48-91A9-C891F12B5750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910586D-87A7-4BCA-AD01-07FE08528EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A8B0BE85-9D20-4728-AB63-3A1F33C5DAD9}"/>
   </bookViews>
@@ -242,13 +242,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -597,10 +597,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="11"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -611,7 +611,7 @@
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -629,13 +629,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="9">
-        <v>3</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -651,8 +651,8 @@
       <c r="E5" s="10">
         <v>4</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -668,8 +668,8 @@
       <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -685,8 +685,8 @@
       <c r="E7" s="10">
         <v>0</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -702,8 +702,8 @@
       <c r="E8" s="10">
         <v>1</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -719,8 +719,8 @@
       <c r="E9" s="10">
         <v>0</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
@@ -736,8 +736,8 @@
       <c r="E10" s="10">
         <v>0</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
@@ -753,8 +753,8 @@
       <c r="E11" s="10">
         <v>0</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -770,8 +770,8 @@
       <c r="E12" s="10">
         <v>0</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
@@ -779,8 +779,8 @@
       <c r="C13" s="7"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -788,8 +788,8 @@
       <c r="C14" s="7"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
@@ -797,8 +797,8 @@
       <c r="C15" s="7"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -806,8 +806,8 @@
       <c r="C16" s="7"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
@@ -815,8 +815,8 @@
       <c r="C17" s="7"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
@@ -824,8 +824,8 @@
       <c r="C18" s="7"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
@@ -833,8 +833,8 @@
       <c r="C19" s="7"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
@@ -842,8 +842,8 @@
       <c r="C20" s="7"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
